--- a/plantillas/consulta/Proyectos_Participantes.xlsx
+++ b/plantillas/consulta/Proyectos_Participantes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E7215F-42A7-4635-8B1D-6F693E9A7194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B6592B-A33F-4311-B295-3D5FACF1C346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,10 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>DIRECCIÓN EJECUTIVA DE ORGANIZACIÓN ELECTORAL Y GEOESTADÍSTICA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Distrito</t>
   </si>
@@ -70,9 +67,6 @@
   </si>
   <si>
     <t>No. del Proyecto Específico</t>
-  </si>
-  <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
   </si>
 </sst>
 </file>
@@ -557,9 +551,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>0</v>
-      </c>
+      <c r="A2" s="10"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -568,10 +560,8 @@
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
-        <v>13</v>
-      </c>
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -592,7 +582,7 @@
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -604,7 +594,7 @@
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -633,38 +623,38 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
       <c r="H9" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="54.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="G11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/plantillas/consulta/Proyectos_Participantes.xlsx
+++ b/plantillas/consulta/Proyectos_Participantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B6592B-A33F-4311-B295-3D5FACF1C346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A1093A-1F3E-4338-B8E7-68C1DF20B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Nombre del Proyecto Específico</t>
   </si>
   <si>
-    <t>Rubro General o Destino</t>
-  </si>
-  <si>
     <t>titulo1</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>No. del Proyecto Específico</t>
+  </si>
+  <si>
+    <t>Destino de los recursos</t>
   </si>
 </sst>
 </file>
@@ -582,7 +582,7 @@
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -636,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>4</v>
@@ -648,10 +648,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>6</v>

--- a/plantillas/consulta/Proyectos_Participantes.xlsx
+++ b/plantillas/consulta/Proyectos_Participantes.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A1093A-1F3E-4338-B8E7-68C1DF20B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
